--- a/apps/web/public/templates/empresas-modelo.xlsx
+++ b/apps/web/public/templates/empresas-modelo.xlsx
@@ -91,7 +91,7 @@
     <t>PJ</t>
   </si>
   <si>
-    <t>12345678000199</t>
+    <t>11222333000181</t>
   </si>
   <si>
     <t>contato@medisa.com.br</t>
@@ -130,7 +130,7 @@
     <t>Clinica Exemplo LTDA</t>
   </si>
   <si>
-    <t>98765432000188</t>
+    <t>99888777000100</t>
   </si>
   <si>
     <t>60000000</t>
